--- a/AAII_Financials/Quarterly/WMPN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WMPN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
   <si>
     <t>WMPN</t>
   </si>
@@ -656,165 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42004</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>41912</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>41729</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E8" s="3">
         <v>8000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>7600</v>
       </c>
       <c r="G8" s="3">
         <v>7600</v>
       </c>
       <c r="H8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I8" s="3">
         <v>7100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6000</v>
-      </c>
-      <c r="M8" s="3">
-        <v>6200</v>
       </c>
       <c r="N8" s="3">
         <v>6200</v>
       </c>
       <c r="O8" s="3">
+        <v>6200</v>
+      </c>
+      <c r="P8" s="3">
         <v>6800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3200</v>
-      </c>
-      <c r="T8" s="3">
-        <v>3100</v>
       </c>
       <c r="U8" s="3">
         <v>3100</v>
       </c>
       <c r="V8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="W8" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -875,8 +881,11 @@
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -937,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1023,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1147,8 +1166,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1168,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>-100</v>
@@ -1197,8 +1219,8 @@
       <c r="R15" s="3">
         <v>-100</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
+      <c r="S15" s="3">
+        <v>-100</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>5</v>
@@ -1209,8 +1231,11 @@
       <c r="V15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,58 +1255,59 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>700</v>
       </c>
       <c r="L17" s="3">
         <v>700</v>
       </c>
       <c r="M17" s="3">
+        <v>700</v>
+      </c>
+      <c r="N17" s="3">
         <v>800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1300</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1000</v>
       </c>
       <c r="T17" s="3">
         <v>1000</v>
@@ -1290,63 +1316,66 @@
         <v>1000</v>
       </c>
       <c r="V17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W17" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E18" s="3">
         <v>4700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2200</v>
-      </c>
-      <c r="T18" s="3">
-        <v>2100</v>
       </c>
       <c r="U18" s="3">
         <v>2100</v>
@@ -1354,8 +1383,11 @@
       <c r="V18" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,109 +1410,113 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4600</v>
+        <v>-4300</v>
       </c>
       <c r="E20" s="3">
         <v>-4600</v>
       </c>
       <c r="F20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="G20" s="3">
         <v>-5400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-4200</v>
       </c>
       <c r="L20" s="3">
         <v>-4200</v>
       </c>
       <c r="M20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="N20" s="3">
         <v>-4600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>200</v>
+      </c>
+      <c r="E21" s="3">
         <v>400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1502,8 +1538,11 @@
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1564,132 +1603,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
         <v>200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1000</v>
-      </c>
-      <c r="S23" s="3">
-        <v>900</v>
       </c>
       <c r="T23" s="3">
         <v>900</v>
       </c>
       <c r="U23" s="3">
+        <v>900</v>
+      </c>
+      <c r="V23" s="3">
         <v>1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
-      </c>
-      <c r="S24" s="3">
-        <v>300</v>
       </c>
       <c r="T24" s="3">
         <v>300</v>
       </c>
       <c r="U24" s="3">
+        <v>300</v>
+      </c>
+      <c r="V24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>800</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1200</v>
       </c>
       <c r="L26" s="3">
         <v>1200</v>
       </c>
       <c r="M26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N26" s="3">
         <v>700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
-      </c>
-      <c r="S26" s="3">
-        <v>600</v>
       </c>
       <c r="T26" s="3">
         <v>600</v>
       </c>
       <c r="U26" s="3">
+        <v>600</v>
+      </c>
+      <c r="V26" s="3">
         <v>1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>800</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1200</v>
       </c>
       <c r="L27" s="3">
         <v>1200</v>
       </c>
       <c r="M27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N27" s="3">
         <v>700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
-      </c>
-      <c r="S27" s="3">
-        <v>600</v>
       </c>
       <c r="T27" s="3">
         <v>600</v>
       </c>
       <c r="U27" s="3">
+        <v>600</v>
+      </c>
+      <c r="V27" s="3">
         <v>1000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4600</v>
+        <v>4300</v>
       </c>
       <c r="E32" s="3">
         <v>4600</v>
       </c>
       <c r="F32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G32" s="3">
         <v>5400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>4200</v>
       </c>
       <c r="L32" s="3">
         <v>4200</v>
       </c>
       <c r="M32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N32" s="3">
         <v>4600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>800</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1200</v>
       </c>
       <c r="L33" s="3">
         <v>1200</v>
       </c>
       <c r="M33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N33" s="3">
         <v>700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
-      </c>
-      <c r="S33" s="3">
-        <v>600</v>
       </c>
       <c r="T33" s="3">
         <v>600</v>
       </c>
       <c r="U33" s="3">
+        <v>600</v>
+      </c>
+      <c r="V33" s="3">
         <v>1000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>800</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1200</v>
       </c>
       <c r="L35" s="3">
         <v>1200</v>
       </c>
       <c r="M35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N35" s="3">
         <v>700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
-      </c>
-      <c r="S35" s="3">
-        <v>600</v>
       </c>
       <c r="T35" s="3">
         <v>600</v>
       </c>
       <c r="U35" s="3">
+        <v>600</v>
+      </c>
+      <c r="V35" s="3">
         <v>1000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42004</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>41912</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>41729</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,112 +2570,116 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E41" s="3">
         <v>7200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8800</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T41" s="3">
         <v>8800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E42" s="3">
         <v>13900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>14000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>32500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>48100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>58300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>123500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>162400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>175900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>68100</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>5</v>
       </c>
@@ -2609,8 +2698,11 @@
       <c r="V42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2671,8 +2763,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2733,8 +2828,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2795,8 +2893,11 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2857,40 +2958,43 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E47" s="3">
         <v>1700</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1600</v>
       </c>
       <c r="F47" s="3">
         <v>1600</v>
       </c>
       <c r="G47" s="3">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H47" s="3">
         <v>2000</v>
       </c>
       <c r="I47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J47" s="3">
         <v>2300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2400</v>
-      </c>
-      <c r="K47" s="3">
-        <v>2600</v>
       </c>
       <c r="L47" s="3">
         <v>2600</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
+      <c r="M47" s="3">
+        <v>2600</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
@@ -2907,8 +3011,8 @@
       <c r="R47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -2919,49 +3023,52 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E48" s="3">
         <v>16400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>18300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>18500</v>
-      </c>
-      <c r="J48" s="3">
-        <v>13400</v>
       </c>
       <c r="K48" s="3">
         <v>13400</v>
       </c>
       <c r="L48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="M48" s="3">
         <v>13500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13400</v>
-      </c>
-      <c r="N48" s="3">
-        <v>13500</v>
       </c>
       <c r="O48" s="3">
         <v>13500</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
+      <c r="P48" s="3">
+        <v>13500</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
@@ -2981,8 +3088,11 @@
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2990,40 +3100,40 @@
         <v>5300</v>
       </c>
       <c r="E49" s="3">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="F49" s="3">
         <v>5400</v>
       </c>
       <c r="G49" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="H49" s="3">
         <v>5500</v>
       </c>
       <c r="I49" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="J49" s="3">
         <v>5600</v>
       </c>
       <c r="K49" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="L49" s="3">
         <v>5700</v>
       </c>
       <c r="M49" s="3">
+        <v>5700</v>
+      </c>
+      <c r="N49" s="3">
         <v>5800</v>
-      </c>
-      <c r="N49" s="3">
-        <v>5900</v>
       </c>
       <c r="O49" s="3">
         <v>5900</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
+      <c r="P49" s="3">
+        <v>5900</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,50 +3283,53 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E52" s="3">
         <v>11100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>826000</v>
+      </c>
+      <c r="E54" s="3">
         <v>830000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>847600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>862400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>870900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>851500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>880000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>869000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>834000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>822900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>822400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>817400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>746500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>323800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>315300</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S54" s="3">
-        <v>315300</v>
+      <c r="S54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T54" s="3">
         <v>315300</v>
       </c>
       <c r="U54" s="3">
+        <v>315300</v>
+      </c>
+      <c r="V54" s="3">
         <v>311500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>311100</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,8 +3530,9 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3463,8 +3593,11 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3525,50 +3658,53 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E59" s="3">
         <v>14400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8200</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3587,8 +3723,11 @@
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3649,8 +3788,11 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3711,8 +3853,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3773,8 +3918,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,50 +4113,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>697100</v>
+      </c>
+      <c r="E66" s="3">
         <v>693600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>686800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>688300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>691700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>670300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>687600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>662700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>620100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>609900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>605500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>602400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>649300</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4021,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,50 +4463,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>58100</v>
+      </c>
+      <c r="E72" s="3">
         <v>58400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>58800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>58900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>58200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>57600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>56900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>56300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>55100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>58500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>57800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>56800</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4355,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>128900</v>
+      </c>
+      <c r="E76" s="3">
         <v>136400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>160700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>174000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>179200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>181200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>192300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>206300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>213900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>213000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>216900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>215000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>97200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>59200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>58400</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T76" s="3">
         <v>58400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>60000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>59800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42004</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>41912</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>41729</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>800</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1200</v>
       </c>
       <c r="L81" s="3">
         <v>1200</v>
       </c>
       <c r="M81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N81" s="3">
         <v>700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
-      </c>
-      <c r="S81" s="3">
-        <v>600</v>
       </c>
       <c r="T81" s="3">
         <v>600</v>
       </c>
       <c r="U81" s="3">
+        <v>600</v>
+      </c>
+      <c r="V81" s="3">
         <v>1000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4827,16 +5025,16 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>300</v>
       </c>
       <c r="G83" s="3">
+        <v>300</v>
+      </c>
+      <c r="H83" s="3">
         <v>400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>300</v>
@@ -4856,8 +5054,8 @@
       <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
+      <c r="O83" s="3">
+        <v>300</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
@@ -4874,14 +5072,17 @@
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,47 +5403,50 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
         <v>400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2100</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5246,14 +5462,17 @@
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,19 +5495,20 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -5297,7 +5517,7 @@
         <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-200</v>
@@ -5306,17 +5526,17 @@
         <v>-200</v>
       </c>
       <c r="L91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5332,14 +5552,17 @@
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,8 +5688,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5471,38 +5700,38 @@
         <v>10300</v>
       </c>
       <c r="E94" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F94" s="3">
         <v>12000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>12300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-44600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-40100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-79100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-36900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>20800</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
@@ -5518,14 +5747,17 @@
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5557,7 +5790,7 @@
         <v>-300</v>
       </c>
       <c r="E96" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="F96" s="3">
         <v>-400</v>
@@ -5572,17 +5805,17 @@
         <v>-400</v>
       </c>
       <c r="J96" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K96" s="3">
         <v>-200</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-4600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,47 +6038,50 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>16600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-22700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>21300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>36600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>10400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>70500</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
@@ -5852,14 +6097,17 @@
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5920,47 +6168,50 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>700</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-17000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-22100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-67300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-40800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>93300</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
@@ -5976,10 +6227,13 @@
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WMPN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WMPN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
   <si>
     <t>WMPN</t>
   </si>
@@ -656,171 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42004</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>41912</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>41729</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E8" s="3">
         <v>8100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>7600</v>
       </c>
       <c r="H8" s="3">
         <v>7600</v>
       </c>
       <c r="I8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="J8" s="3">
         <v>7100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6000</v>
-      </c>
-      <c r="N8" s="3">
-        <v>6200</v>
       </c>
       <c r="O8" s="3">
         <v>6200</v>
       </c>
       <c r="P8" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Q8" s="3">
         <v>6800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3200</v>
-      </c>
-      <c r="U8" s="3">
-        <v>3100</v>
       </c>
       <c r="V8" s="3">
         <v>3100</v>
       </c>
       <c r="W8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="X8" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -884,8 +891,11 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -949,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1169,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1193,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>-100</v>
@@ -1222,8 +1245,8 @@
       <c r="S15" s="3">
         <v>-100</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
+      <c r="T15" s="3">
+        <v>-100</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>5</v>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,61 +1282,62 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E17" s="3">
         <v>3900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
-      </c>
-      <c r="L17" s="3">
-        <v>700</v>
       </c>
       <c r="M17" s="3">
         <v>700</v>
       </c>
       <c r="N17" s="3">
+        <v>700</v>
+      </c>
+      <c r="O17" s="3">
         <v>800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1300</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1000</v>
       </c>
       <c r="U17" s="3">
         <v>1000</v>
@@ -1319,66 +1346,69 @@
         <v>1000</v>
       </c>
       <c r="W17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X17" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E18" s="3">
         <v>4200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2200</v>
-      </c>
-      <c r="U18" s="3">
-        <v>2100</v>
       </c>
       <c r="V18" s="3">
         <v>2100</v>
@@ -1386,8 +1416,11 @@
       <c r="W18" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,115 +1444,119 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-4600</v>
       </c>
       <c r="F20" s="3">
         <v>-4600</v>
       </c>
       <c r="G20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="H20" s="3">
         <v>-5400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-4200</v>
       </c>
       <c r="M20" s="3">
         <v>-4200</v>
       </c>
       <c r="N20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="O20" s="3">
         <v>-4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
         <v>200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1541,8 +1578,11 @@
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1606,8 +1646,11 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1615,129 +1658,135 @@
         <v>-100</v>
       </c>
       <c r="E23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="3">
         <v>200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1000</v>
-      </c>
-      <c r="T23" s="3">
-        <v>900</v>
       </c>
       <c r="U23" s="3">
         <v>900</v>
       </c>
       <c r="V23" s="3">
+        <v>900</v>
+      </c>
+      <c r="W23" s="3">
         <v>1500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>200</v>
       </c>
       <c r="L24" s="3">
         <v>200</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
-      </c>
-      <c r="T24" s="3">
-        <v>300</v>
       </c>
       <c r="U24" s="3">
         <v>300</v>
       </c>
       <c r="V24" s="3">
+        <v>300</v>
+      </c>
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
-      </c>
-      <c r="L26" s="3">
-        <v>1200</v>
       </c>
       <c r="M26" s="3">
         <v>1200</v>
       </c>
       <c r="N26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>800</v>
-      </c>
-      <c r="T26" s="3">
-        <v>600</v>
       </c>
       <c r="U26" s="3">
         <v>600</v>
       </c>
       <c r="V26" s="3">
+        <v>600</v>
+      </c>
+      <c r="W26" s="3">
         <v>1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>800</v>
-      </c>
-      <c r="L27" s="3">
-        <v>1200</v>
       </c>
       <c r="M27" s="3">
         <v>1200</v>
       </c>
       <c r="N27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O27" s="3">
         <v>700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>800</v>
-      </c>
-      <c r="T27" s="3">
-        <v>600</v>
       </c>
       <c r="U27" s="3">
         <v>600</v>
       </c>
       <c r="V27" s="3">
+        <v>600</v>
+      </c>
+      <c r="W27" s="3">
         <v>1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E32" s="3">
         <v>4300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>4600</v>
       </c>
       <c r="F32" s="3">
         <v>4600</v>
       </c>
       <c r="G32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H32" s="3">
         <v>5400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>4200</v>
       </c>
       <c r="M32" s="3">
         <v>4200</v>
       </c>
       <c r="N32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="O32" s="3">
         <v>4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>800</v>
-      </c>
-      <c r="L33" s="3">
-        <v>1200</v>
       </c>
       <c r="M33" s="3">
         <v>1200</v>
       </c>
       <c r="N33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O33" s="3">
         <v>700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>800</v>
-      </c>
-      <c r="T33" s="3">
-        <v>600</v>
       </c>
       <c r="U33" s="3">
         <v>600</v>
       </c>
       <c r="V33" s="3">
+        <v>600</v>
+      </c>
+      <c r="W33" s="3">
         <v>1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>800</v>
-      </c>
-      <c r="L35" s="3">
-        <v>1200</v>
       </c>
       <c r="M35" s="3">
         <v>1200</v>
       </c>
       <c r="N35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O35" s="3">
         <v>700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>800</v>
-      </c>
-      <c r="T35" s="3">
-        <v>600</v>
       </c>
       <c r="U35" s="3">
         <v>600</v>
       </c>
       <c r="V35" s="3">
+        <v>600</v>
+      </c>
+      <c r="W35" s="3">
         <v>1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42004</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>41912</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>41729</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,118 +2657,122 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E41" s="3">
         <v>6100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>23600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8800</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U41" s="3">
         <v>8800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E42" s="3">
         <v>14800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>32500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>48100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>58300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>123500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>162400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>175900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>68100</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
@@ -2701,8 +2791,11 @@
       <c r="W42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2766,8 +2859,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2831,8 +2927,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2896,8 +2995,11 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2961,43 +3063,46 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1700</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1600</v>
       </c>
       <c r="G47" s="3">
         <v>1600</v>
       </c>
       <c r="H47" s="3">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="I47" s="3">
         <v>2000</v>
       </c>
       <c r="J47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K47" s="3">
         <v>2300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2400</v>
-      </c>
-      <c r="L47" s="3">
-        <v>2600</v>
       </c>
       <c r="M47" s="3">
         <v>2600</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
+      <c r="N47" s="3">
+        <v>2600</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
@@ -3014,8 +3119,8 @@
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3026,52 +3131,55 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E48" s="3">
         <v>16100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>18300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>18500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>13400</v>
       </c>
       <c r="L48" s="3">
         <v>13400</v>
       </c>
       <c r="M48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="N48" s="3">
         <v>13500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13400</v>
-      </c>
-      <c r="O48" s="3">
-        <v>13500</v>
       </c>
       <c r="P48" s="3">
         <v>13500</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
+      <c r="Q48" s="3">
+        <v>13500</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
@@ -3091,8 +3199,11 @@
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3103,40 +3214,40 @@
         <v>5300</v>
       </c>
       <c r="F49" s="3">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="G49" s="3">
         <v>5400</v>
       </c>
       <c r="H49" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="I49" s="3">
         <v>5500</v>
       </c>
       <c r="J49" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="K49" s="3">
         <v>5600</v>
       </c>
       <c r="L49" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="M49" s="3">
         <v>5700</v>
       </c>
       <c r="N49" s="3">
+        <v>5700</v>
+      </c>
+      <c r="O49" s="3">
         <v>5800</v>
-      </c>
-      <c r="O49" s="3">
-        <v>5900</v>
       </c>
       <c r="P49" s="3">
         <v>5900</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
+      <c r="Q49" s="3">
+        <v>5900</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>5</v>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,53 +3403,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E52" s="3">
         <v>9000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>833200</v>
+      </c>
+      <c r="E54" s="3">
         <v>826000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>830000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>847600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>862400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>870900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>851500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>880000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>869000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>834000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>822900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>822400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>817400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>746500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>323800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>315300</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T54" s="3">
-        <v>315300</v>
+      <c r="T54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U54" s="3">
         <v>315300</v>
       </c>
       <c r="V54" s="3">
+        <v>315300</v>
+      </c>
+      <c r="W54" s="3">
         <v>311500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>311100</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,8 +3661,9 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3596,8 +3727,11 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3661,8 +3795,11 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3670,44 +3807,44 @@
         <v>13900</v>
       </c>
       <c r="E59" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F59" s="3">
         <v>14400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3726,8 +3863,11 @@
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3791,8 +3931,11 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3856,8 +3999,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,53 +4271,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>707400</v>
+      </c>
+      <c r="E66" s="3">
         <v>697100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>693600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>686800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>688300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>691700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>670300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>687600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>662700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>620100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>609900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>605500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>602400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>649300</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,53 +4637,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E72" s="3">
         <v>58100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>58400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>58600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>58900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>58200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>57600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>56900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>56300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>55100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>58500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>57800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>56800</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>125800</v>
+      </c>
+      <c r="E76" s="3">
         <v>128900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>136400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>160700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>174000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>179200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>181200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>192300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>206300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>213900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>213000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>216900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>215000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>97200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>59200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>58400</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T76" s="3">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U76" s="3">
         <v>58400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>60000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>59800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42004</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>41912</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>41729</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>800</v>
-      </c>
-      <c r="L81" s="3">
-        <v>1200</v>
       </c>
       <c r="M81" s="3">
         <v>1200</v>
       </c>
       <c r="N81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O81" s="3">
         <v>700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>800</v>
-      </c>
-      <c r="T81" s="3">
-        <v>600</v>
       </c>
       <c r="U81" s="3">
         <v>600</v>
       </c>
       <c r="V81" s="3">
+        <v>600</v>
+      </c>
+      <c r="W81" s="3">
         <v>1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5028,16 +5227,16 @@
         <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>300</v>
       </c>
       <c r="H83" s="3">
+        <v>300</v>
+      </c>
+      <c r="I83" s="3">
         <v>400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>300</v>
@@ -5057,8 +5256,8 @@
       <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
+      <c r="P83" s="3">
+        <v>300</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>5</v>
@@ -5075,14 +5274,17 @@
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,50 +5620,53 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
         <v>300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2100</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5465,14 +5682,17 @@
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,22 +5716,23 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
@@ -5520,7 +5741,7 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
@@ -5529,17 +5750,17 @@
         <v>-200</v>
       </c>
       <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5555,14 +5776,17 @@
       <c r="U91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,50 +5918,53 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>10300</v>
+        <v>-6900</v>
       </c>
       <c r="E94" s="3">
         <v>10300</v>
       </c>
       <c r="F94" s="3">
+        <v>10300</v>
+      </c>
+      <c r="G94" s="3">
         <v>12000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>12300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-44600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-40100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-79100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>20800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>5</v>
       </c>
@@ -5750,14 +5980,17 @@
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5793,7 +6027,7 @@
         <v>-300</v>
       </c>
       <c r="F96" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="G96" s="3">
         <v>-400</v>
@@ -5808,17 +6042,17 @@
         <v>-400</v>
       </c>
       <c r="K96" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L96" s="3">
         <v>-200</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-4600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,50 +6284,53 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>16600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-22700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>21300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>36600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>10400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>70500</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6100,14 +6346,17 @@
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6171,50 +6420,53 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-17000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-22100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-67300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-40800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>93300</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6230,10 +6482,13 @@
       <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WMPN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WMPN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>WMPN</t>
   </si>
@@ -656,178 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42004</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>41912</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>41729</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E8" s="3">
         <v>8200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8100</v>
-      </c>
-      <c r="H8" s="3">
-        <v>7600</v>
       </c>
       <c r="I8" s="3">
         <v>7600</v>
       </c>
       <c r="J8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K8" s="3">
         <v>7100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6000</v>
-      </c>
-      <c r="O8" s="3">
-        <v>6200</v>
       </c>
       <c r="P8" s="3">
         <v>6200</v>
       </c>
       <c r="Q8" s="3">
+        <v>6200</v>
+      </c>
+      <c r="R8" s="3">
         <v>6800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3200</v>
-      </c>
-      <c r="V8" s="3">
-        <v>3100</v>
       </c>
       <c r="W8" s="3">
         <v>3100</v>
       </c>
       <c r="X8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Y8" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -894,8 +901,11 @@
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1141,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1219,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>-100</v>
@@ -1248,8 +1271,8 @@
       <c r="T15" s="3">
         <v>-100</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
+      <c r="U15" s="3">
+        <v>-100</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>5</v>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,64 +1309,65 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
-      </c>
-      <c r="M17" s="3">
-        <v>700</v>
       </c>
       <c r="N17" s="3">
         <v>700</v>
       </c>
       <c r="O17" s="3">
+        <v>700</v>
+      </c>
+      <c r="P17" s="3">
         <v>800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1300</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1000</v>
       </c>
       <c r="V17" s="3">
         <v>1000</v>
@@ -1349,69 +1376,72 @@
         <v>1000</v>
       </c>
       <c r="X17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y17" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E18" s="3">
         <v>4600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2200</v>
-      </c>
-      <c r="V18" s="3">
-        <v>2100</v>
       </c>
       <c r="W18" s="3">
         <v>2100</v>
@@ -1419,8 +1449,11 @@
       <c r="X18" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,8 +1478,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1454,112 +1488,115 @@
         <v>-4600</v>
       </c>
       <c r="E20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-4300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-4600</v>
       </c>
       <c r="G20" s="3">
         <v>-4600</v>
       </c>
       <c r="H20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I20" s="3">
         <v>-5400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-4200</v>
       </c>
       <c r="N20" s="3">
         <v>-4200</v>
       </c>
       <c r="O20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="P20" s="3">
         <v>-4600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1581,8 +1618,11 @@
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,144 +1689,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="E23" s="3">
         <v>-100</v>
       </c>
       <c r="F23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G23" s="3">
         <v>200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1000</v>
-      </c>
-      <c r="U23" s="3">
-        <v>900</v>
       </c>
       <c r="V23" s="3">
         <v>900</v>
       </c>
       <c r="W23" s="3">
+        <v>900</v>
+      </c>
+      <c r="X23" s="3">
         <v>1500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
-      </c>
-      <c r="L24" s="3">
-        <v>200</v>
       </c>
       <c r="M24" s="3">
         <v>200</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
-      </c>
-      <c r="U24" s="3">
-        <v>300</v>
       </c>
       <c r="V24" s="3">
         <v>300</v>
       </c>
       <c r="W24" s="3">
+        <v>300</v>
+      </c>
+      <c r="X24" s="3">
         <v>500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
         <v>100</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>800</v>
-      </c>
-      <c r="M26" s="3">
-        <v>1200</v>
       </c>
       <c r="N26" s="3">
         <v>1200</v>
       </c>
       <c r="O26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P26" s="3">
         <v>700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>800</v>
-      </c>
-      <c r="U26" s="3">
-        <v>600</v>
       </c>
       <c r="V26" s="3">
         <v>600</v>
       </c>
       <c r="W26" s="3">
+        <v>600</v>
+      </c>
+      <c r="X26" s="3">
         <v>1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
         <v>100</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>800</v>
-      </c>
-      <c r="M27" s="3">
-        <v>1200</v>
       </c>
       <c r="N27" s="3">
         <v>1200</v>
       </c>
       <c r="O27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P27" s="3">
         <v>700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>800</v>
-      </c>
-      <c r="U27" s="3">
-        <v>600</v>
       </c>
       <c r="V27" s="3">
         <v>600</v>
       </c>
       <c r="W27" s="3">
+        <v>600</v>
+      </c>
+      <c r="X27" s="3">
         <v>1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,8 +2328,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2270,135 +2340,141 @@
         <v>4600</v>
       </c>
       <c r="E32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F32" s="3">
         <v>4300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>4600</v>
       </c>
       <c r="G32" s="3">
         <v>4600</v>
       </c>
       <c r="H32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I32" s="3">
         <v>5400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>4200</v>
       </c>
       <c r="N32" s="3">
         <v>4200</v>
       </c>
       <c r="O32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="P32" s="3">
         <v>4600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
         <v>100</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
-      </c>
-      <c r="M33" s="3">
-        <v>1200</v>
       </c>
       <c r="N33" s="3">
         <v>1200</v>
       </c>
       <c r="O33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P33" s="3">
         <v>700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>800</v>
-      </c>
-      <c r="U33" s="3">
-        <v>600</v>
       </c>
       <c r="V33" s="3">
         <v>600</v>
       </c>
       <c r="W33" s="3">
+        <v>600</v>
+      </c>
+      <c r="X33" s="3">
         <v>1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
         <v>100</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
-      </c>
-      <c r="M35" s="3">
-        <v>1200</v>
       </c>
       <c r="N35" s="3">
         <v>1200</v>
       </c>
       <c r="O35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P35" s="3">
         <v>700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>800</v>
-      </c>
-      <c r="U35" s="3">
-        <v>600</v>
       </c>
       <c r="V35" s="3">
         <v>600</v>
       </c>
       <c r="W35" s="3">
+        <v>600</v>
+      </c>
+      <c r="X35" s="3">
         <v>1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42004</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>41912</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>41729</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,124 +2744,128 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E41" s="3">
         <v>5800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>23600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8800</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3">
         <v>8800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>13300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E42" s="3">
         <v>16000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>15400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>14000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>32500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>48100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>58300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>123500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>162400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>175900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>68100</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
@@ -2794,8 +2884,11 @@
       <c r="X42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2862,8 +2955,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2930,8 +3026,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2998,8 +3097,11 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3066,8 +3168,11 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3075,37 +3180,37 @@
         <v>2000</v>
       </c>
       <c r="E47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1700</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1600</v>
       </c>
       <c r="H47" s="3">
         <v>1600</v>
       </c>
       <c r="I47" s="3">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="J47" s="3">
         <v>2000</v>
       </c>
       <c r="K47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L47" s="3">
         <v>2300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2400</v>
-      </c>
-      <c r="M47" s="3">
-        <v>2600</v>
       </c>
       <c r="N47" s="3">
         <v>2600</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
+      <c r="O47" s="3">
+        <v>2600</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>5</v>
@@ -3122,8 +3227,8 @@
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3134,55 +3239,58 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E48" s="3">
         <v>15800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>18000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>18300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>13400</v>
       </c>
       <c r="M48" s="3">
         <v>13400</v>
       </c>
       <c r="N48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="O48" s="3">
         <v>13500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13400</v>
-      </c>
-      <c r="P48" s="3">
-        <v>13500</v>
       </c>
       <c r="Q48" s="3">
         <v>13500</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
+      <c r="R48" s="3">
+        <v>13500</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
@@ -3202,13 +3310,16 @@
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="E49" s="3">
         <v>5300</v>
@@ -3217,40 +3328,40 @@
         <v>5300</v>
       </c>
       <c r="G49" s="3">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="H49" s="3">
         <v>5400</v>
       </c>
       <c r="I49" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="J49" s="3">
         <v>5500</v>
       </c>
       <c r="K49" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="L49" s="3">
         <v>5600</v>
       </c>
       <c r="M49" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="N49" s="3">
         <v>5700</v>
       </c>
       <c r="O49" s="3">
+        <v>5700</v>
+      </c>
+      <c r="P49" s="3">
         <v>5800</v>
-      </c>
-      <c r="P49" s="3">
-        <v>5900</v>
       </c>
       <c r="Q49" s="3">
         <v>5900</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
+      <c r="R49" s="3">
+        <v>5900</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,56 +3523,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E52" s="3">
         <v>9300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>818700</v>
+      </c>
+      <c r="E54" s="3">
         <v>833200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>826000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>830000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>847600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>862400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>870900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>851500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>880000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>869000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>834000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>822900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>822400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>817400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>746500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>323800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>315300</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U54" s="3">
-        <v>315300</v>
+      <c r="U54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V54" s="3">
         <v>315300</v>
       </c>
       <c r="W54" s="3">
+        <v>315300</v>
+      </c>
+      <c r="X54" s="3">
         <v>311500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>311100</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,8 +3792,9 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3730,8 +3861,11 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3798,56 +3932,59 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13900</v>
+        <v>13400</v>
       </c>
       <c r="E59" s="3">
         <v>13900</v>
       </c>
       <c r="F59" s="3">
+        <v>13900</v>
+      </c>
+      <c r="G59" s="3">
         <v>14400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3866,8 +4003,11 @@
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3934,8 +4074,11 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4002,8 +4145,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,56 +4429,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>694100</v>
+      </c>
+      <c r="E66" s="3">
         <v>707400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>697100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>693600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>686800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>688300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>691700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>670300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>687600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>662700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>620100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>609900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>605500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>602400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>649300</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,56 +4811,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E72" s="3">
         <v>58000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>58100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>58800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>58600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>58900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>58200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>57600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>56900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>56300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>55100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>58500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>57800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>56800</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E76" s="3">
         <v>125800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>128900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>136400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>160700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>174000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>179200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>181200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>192300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>206300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>213900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>213000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>216900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>215000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>97200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>59200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>58400</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3">
         <v>58400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>60000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>59800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42004</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>41912</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>41729</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
         <v>100</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
-      </c>
-      <c r="M81" s="3">
-        <v>1200</v>
       </c>
       <c r="N81" s="3">
         <v>1200</v>
       </c>
       <c r="O81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P81" s="3">
         <v>700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>800</v>
-      </c>
-      <c r="U81" s="3">
-        <v>600</v>
       </c>
       <c r="V81" s="3">
         <v>600</v>
       </c>
       <c r="W81" s="3">
+        <v>600</v>
+      </c>
+      <c r="X81" s="3">
         <v>1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5230,16 +5429,16 @@
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>300</v>
       </c>
       <c r="I83" s="3">
+        <v>300</v>
+      </c>
+      <c r="J83" s="3">
         <v>400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
@@ -5259,8 +5458,8 @@
       <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
+      <c r="Q83" s="3">
+        <v>300</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
@@ -5277,14 +5476,17 @@
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,53 +5837,56 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2100</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5685,14 +5902,17 @@
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +5937,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5726,16 +5947,16 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -5744,7 +5965,7 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
@@ -5753,17 +5974,17 @@
         <v>-200</v>
       </c>
       <c r="N91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5779,14 +6000,17 @@
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,53 +6148,56 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6900</v>
-      </c>
-      <c r="E94" s="3">
-        <v>10300</v>
       </c>
       <c r="F94" s="3">
         <v>10300</v>
       </c>
       <c r="G94" s="3">
+        <v>10300</v>
+      </c>
+      <c r="H94" s="3">
         <v>12000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>12300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-44600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-40100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-79100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-36900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>20800</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
@@ -5983,14 +6213,17 @@
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6030,7 +6264,7 @@
         <v>-300</v>
       </c>
       <c r="G96" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="H96" s="3">
         <v>-400</v>
@@ -6045,17 +6279,17 @@
         <v>-400</v>
       </c>
       <c r="L96" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M96" s="3">
         <v>-200</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-4600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,53 +6530,56 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E100" s="3">
         <v>7600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>16600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-22700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>21300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>36600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>10400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>70500</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6349,14 +6595,17 @@
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,53 +6672,56 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-17000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-22100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-67300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-40800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>93300</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6485,10 +6737,13 @@
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WMPN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WMPN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>WMPN</t>
   </si>
@@ -656,185 +656,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42004</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>41912</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>41729</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8300</v>
+        <v>5200</v>
       </c>
       <c r="E8" s="3">
-        <v>8200</v>
+        <v>4900</v>
       </c>
       <c r="F8" s="3">
-        <v>8100</v>
+        <v>5200</v>
       </c>
       <c r="G8" s="3">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H8" s="3">
-        <v>8100</v>
+        <v>5400</v>
       </c>
       <c r="I8" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J8" s="3">
+        <v>5700</v>
+      </c>
+      <c r="K8" s="3">
         <v>7600</v>
       </c>
-      <c r="J8" s="3">
-        <v>7600</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6000</v>
-      </c>
-      <c r="P8" s="3">
-        <v>6200</v>
       </c>
       <c r="Q8" s="3">
         <v>6200</v>
       </c>
       <c r="R8" s="3">
+        <v>6200</v>
+      </c>
+      <c r="S8" s="3">
         <v>6800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3200</v>
-      </c>
-      <c r="W8" s="3">
-        <v>3100</v>
       </c>
       <c r="X8" s="3">
         <v>3100</v>
       </c>
       <c r="Y8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Z8" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -904,31 +911,34 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -975,8 +985,11 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,31 +1161,34 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1215,37 +1235,40 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3">
         <v>-100</v>
@@ -1274,8 +1297,8 @@
       <c r="U15" s="3">
         <v>-100</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
+      <c r="V15" s="3">
+        <v>-100</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>5</v>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,67 +1336,68 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="E17" s="3">
-        <v>3600</v>
+        <v>5200</v>
       </c>
       <c r="F17" s="3">
-        <v>3900</v>
+        <v>5300</v>
       </c>
       <c r="G17" s="3">
-        <v>3300</v>
+        <v>5000</v>
       </c>
       <c r="H17" s="3">
-        <v>2900</v>
+        <v>5200</v>
       </c>
       <c r="I17" s="3">
-        <v>2100</v>
+        <v>5200</v>
       </c>
       <c r="J17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K17" s="3">
         <v>1500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>600</v>
-      </c>
-      <c r="N17" s="3">
-        <v>700</v>
       </c>
       <c r="O17" s="3">
         <v>700</v>
       </c>
       <c r="P17" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q17" s="3">
         <v>800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1300</v>
-      </c>
-      <c r="V17" s="3">
-        <v>1000</v>
       </c>
       <c r="W17" s="3">
         <v>1000</v>
@@ -1379,72 +1406,75 @@
         <v>1000</v>
       </c>
       <c r="Y17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z17" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4300</v>
+        <v>-100</v>
       </c>
       <c r="E18" s="3">
-        <v>4600</v>
+        <v>-300</v>
       </c>
       <c r="F18" s="3">
-        <v>4200</v>
+        <v>-100</v>
       </c>
       <c r="G18" s="3">
-        <v>4700</v>
+        <v>0</v>
       </c>
       <c r="H18" s="3">
+        <v>200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>700</v>
+      </c>
+      <c r="J18" s="3">
+        <v>200</v>
+      </c>
+      <c r="K18" s="3">
+        <v>6100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M18" s="3">
+        <v>6200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O18" s="3">
+        <v>5500</v>
+      </c>
+      <c r="P18" s="3">
+        <v>5300</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>5400</v>
+      </c>
+      <c r="R18" s="3">
+        <v>5300</v>
+      </c>
+      <c r="S18" s="3">
+        <v>5600</v>
+      </c>
+      <c r="T18" s="3">
         <v>5200</v>
       </c>
-      <c r="I18" s="3">
-        <v>5500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>6100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>6300</v>
-      </c>
-      <c r="L18" s="3">
-        <v>6200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>6000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>5500</v>
-      </c>
-      <c r="O18" s="3">
-        <v>5300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>5400</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>5300</v>
-      </c>
-      <c r="R18" s="3">
-        <v>5600</v>
-      </c>
-      <c r="S18" s="3">
-        <v>5200</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2200</v>
-      </c>
-      <c r="W18" s="3">
-        <v>2100</v>
       </c>
       <c r="X18" s="3">
         <v>2100</v>
@@ -1452,8 +1482,11 @@
       <c r="Y18" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,127 +1512,131 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4600</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-4600</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>-4300</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-4600</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-4600</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-5400</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-4800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-4200</v>
       </c>
       <c r="O20" s="3">
         <v>-4200</v>
       </c>
       <c r="P20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1621,31 +1658,34 @@
       <c r="Y21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1692,79 +1732,85 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-300</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-100</v>
       </c>
       <c r="F23" s="3">
         <v>-100</v>
       </c>
       <c r="G23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H23" s="3">
         <v>200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1000</v>
-      </c>
-      <c r="V23" s="3">
-        <v>900</v>
       </c>
       <c r="W23" s="3">
         <v>900</v>
       </c>
       <c r="X23" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1772,70 +1818,73 @@
         <v>-100</v>
       </c>
       <c r="E24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>200</v>
       </c>
       <c r="N24" s="3">
         <v>200</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
-      </c>
-      <c r="V24" s="3">
-        <v>300</v>
       </c>
       <c r="W24" s="3">
         <v>300</v>
       </c>
       <c r="X24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y24" s="3">
         <v>500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>1200</v>
       </c>
       <c r="O26" s="3">
         <v>1200</v>
       </c>
       <c r="P26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q26" s="3">
         <v>700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>800</v>
-      </c>
-      <c r="V26" s="3">
-        <v>600</v>
       </c>
       <c r="W26" s="3">
         <v>600</v>
       </c>
       <c r="X26" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y26" s="3">
         <v>1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>100</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>800</v>
-      </c>
-      <c r="N27" s="3">
-        <v>1200</v>
       </c>
       <c r="O27" s="3">
         <v>1200</v>
       </c>
       <c r="P27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>800</v>
-      </c>
-      <c r="V27" s="3">
-        <v>600</v>
       </c>
       <c r="W27" s="3">
         <v>600</v>
       </c>
       <c r="X27" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y27" s="3">
         <v>1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>4800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>4200</v>
       </c>
       <c r="O32" s="3">
         <v>4200</v>
       </c>
       <c r="P32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>4600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>100</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
-      </c>
-      <c r="N33" s="3">
-        <v>1200</v>
       </c>
       <c r="O33" s="3">
         <v>1200</v>
       </c>
       <c r="P33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>800</v>
-      </c>
-      <c r="V33" s="3">
-        <v>600</v>
       </c>
       <c r="W33" s="3">
         <v>600</v>
       </c>
       <c r="X33" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y33" s="3">
         <v>1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>100</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
-      </c>
-      <c r="N35" s="3">
-        <v>1200</v>
       </c>
       <c r="O35" s="3">
         <v>1200</v>
       </c>
       <c r="P35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>800</v>
-      </c>
-      <c r="V35" s="3">
-        <v>600</v>
       </c>
       <c r="W35" s="3">
         <v>600</v>
       </c>
       <c r="X35" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y35" s="3">
         <v>1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42004</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>41912</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>41729</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,130 +2831,134 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6500</v>
+        <v>26500</v>
       </c>
       <c r="E41" s="3">
-        <v>5800</v>
+        <v>20200</v>
       </c>
       <c r="F41" s="3">
-        <v>6100</v>
+        <v>18000</v>
       </c>
       <c r="G41" s="3">
-        <v>7200</v>
+        <v>17500</v>
       </c>
       <c r="H41" s="3">
-        <v>7700</v>
+        <v>18000</v>
       </c>
       <c r="I41" s="3">
-        <v>4800</v>
+        <v>20800</v>
       </c>
       <c r="J41" s="3">
+        <v>19900</v>
+      </c>
+      <c r="K41" s="3">
         <v>7900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>23600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8800</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W41" s="3">
         <v>8800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>13300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>15200</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>16000</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>14800</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>13900</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>14700</v>
+        <v>100</v>
       </c>
       <c r="I42" s="3">
-        <v>9600</v>
+        <v>600</v>
       </c>
       <c r="J42" s="3">
+        <v>600</v>
+      </c>
+      <c r="K42" s="3">
         <v>15400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>14000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>32500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>48100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>58300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>123500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>162400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>175900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>68100</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>5</v>
       </c>
@@ -2887,31 +2977,34 @@
       <c r="Y42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2958,31 +3051,34 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3029,31 +3125,34 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3100,31 +3199,34 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>33800</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>27200</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>25800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>24700</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>25600</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>27600</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3171,49 +3273,52 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2000</v>
+        <v>245700</v>
       </c>
       <c r="E47" s="3">
-        <v>2000</v>
+        <v>248900</v>
       </c>
       <c r="F47" s="3">
-        <v>1900</v>
+        <v>257300</v>
       </c>
       <c r="G47" s="3">
-        <v>1700</v>
+        <v>262500</v>
       </c>
       <c r="H47" s="3">
-        <v>1600</v>
+        <v>258600</v>
       </c>
       <c r="I47" s="3">
-        <v>1600</v>
+        <v>269000</v>
       </c>
       <c r="J47" s="3">
-        <v>2000</v>
+        <v>277300</v>
       </c>
       <c r="K47" s="3">
         <v>2000</v>
       </c>
       <c r="L47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M47" s="3">
         <v>2300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2400</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2600</v>
       </c>
       <c r="O47" s="3">
         <v>2600</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
+      <c r="P47" s="3">
+        <v>2600</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>5</v>
@@ -3230,8 +3335,8 @@
       <c r="U47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3242,58 +3347,61 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E48" s="3">
         <v>15500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>18000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18500</v>
-      </c>
-      <c r="M48" s="3">
-        <v>13400</v>
       </c>
       <c r="N48" s="3">
         <v>13400</v>
       </c>
       <c r="O48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="P48" s="3">
         <v>13500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13400</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>13500</v>
       </c>
       <c r="R48" s="3">
         <v>13500</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
+      <c r="S48" s="3">
+        <v>13500</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
@@ -3313,8 +3421,11 @@
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3322,7 +3433,7 @@
         <v>5200</v>
       </c>
       <c r="E49" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="F49" s="3">
         <v>5300</v>
@@ -3331,40 +3442,40 @@
         <v>5300</v>
       </c>
       <c r="H49" s="3">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="I49" s="3">
         <v>5400</v>
       </c>
       <c r="J49" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="K49" s="3">
         <v>5500</v>
       </c>
       <c r="L49" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="M49" s="3">
         <v>5600</v>
       </c>
       <c r="N49" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="O49" s="3">
         <v>5700</v>
       </c>
       <c r="P49" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Q49" s="3">
         <v>5800</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>5900</v>
       </c>
       <c r="R49" s="3">
         <v>5900</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
+      <c r="S49" s="3">
+        <v>5900</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>5</v>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,59 +3643,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>9600</v>
+        <v>42100</v>
       </c>
       <c r="E52" s="3">
+        <v>41800</v>
+      </c>
+      <c r="F52" s="3">
+        <v>41500</v>
+      </c>
+      <c r="G52" s="3">
+        <v>41200</v>
+      </c>
+      <c r="H52" s="3">
+        <v>40900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>40600</v>
+      </c>
+      <c r="J52" s="3">
+        <v>40300</v>
+      </c>
+      <c r="K52" s="3">
         <v>9300</v>
       </c>
-      <c r="F52" s="3">
-        <v>9000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>11100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>9500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>8900</v>
-      </c>
-      <c r="J52" s="3">
-        <v>9300</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3700</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>812200</v>
+      </c>
+      <c r="E54" s="3">
         <v>818700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>833200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>826000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>830000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>847600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>862400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>870900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>851500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>880000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>869000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>834000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>822900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>822400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>817400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>746500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>323800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>315300</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="3">
-        <v>315300</v>
+      <c r="V54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W54" s="3">
         <v>315300</v>
       </c>
       <c r="X54" s="3">
+        <v>315300</v>
+      </c>
+      <c r="Y54" s="3">
         <v>311500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>311100</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,31 +3923,32 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>629800</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>629800</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>625800</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>626700</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>626500</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>635300</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>632700</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -3864,31 +3995,34 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>48800</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>51800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>38800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3935,59 +4069,62 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>13400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>13900</v>
-      </c>
-      <c r="F59" s="3">
-        <v>13900</v>
-      </c>
-      <c r="G59" s="3">
-        <v>14400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>14300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>14700</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>13600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4006,31 +4143,34 @@
       <c r="Y59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>674000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>683500</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>696000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>685800</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>683700</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>674500</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>676900</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -4077,31 +4217,34 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4148,31 +4291,34 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,59 +4587,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>684000</v>
+      </c>
+      <c r="E66" s="3">
         <v>694100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>707400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>697100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>693600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>686800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>688300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>691700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>670300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>687600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>662700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>620100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>609900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>605500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>602400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>649300</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,59 +4985,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E72" s="3">
         <v>57600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>58000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>58400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>58800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>58600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>58900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>58200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>57600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>56900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>56300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>55100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>58500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>57800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>56800</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>128300</v>
+      </c>
+      <c r="E76" s="3">
         <v>124600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>125800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>128900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>136400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>160700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>174000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>179200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>181200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>192300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>206300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>213900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>213000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>216900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>215000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>97200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>59200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>58400</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W76" s="3">
         <v>58400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>60000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>59800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42004</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>41912</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>41729</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>100</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
-      </c>
-      <c r="N81" s="3">
-        <v>1200</v>
       </c>
       <c r="O81" s="3">
         <v>1200</v>
       </c>
       <c r="P81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>800</v>
-      </c>
-      <c r="V81" s="3">
-        <v>600</v>
       </c>
       <c r="W81" s="3">
         <v>600</v>
       </c>
       <c r="X81" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y81" s="3">
         <v>1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5612,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5429,7 +5628,7 @@
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H83" s="3">
         <v>300</v>
@@ -5438,10 +5637,10 @@
         <v>300</v>
       </c>
       <c r="J83" s="3">
+        <v>300</v>
+      </c>
+      <c r="K83" s="3">
         <v>400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
@@ -5461,8 +5660,8 @@
       <c r="Q83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
+      <c r="R83" s="3">
+        <v>300</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
@@ -5479,14 +5678,17 @@
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,56 +6054,59 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>-400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2100</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5905,14 +6122,17 @@
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
+      <c r="X89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,28 +6158,29 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -5968,7 +6189,7 @@
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>-200</v>
@@ -5977,17 +6198,17 @@
         <v>-200</v>
       </c>
       <c r="O91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6003,14 +6224,17 @@
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,56 +6378,59 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>16800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6900</v>
-      </c>
-      <c r="F94" s="3">
-        <v>10300</v>
       </c>
       <c r="G94" s="3">
         <v>10300</v>
       </c>
       <c r="H94" s="3">
+        <v>10300</v>
+      </c>
+      <c r="I94" s="3">
         <v>12000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>12300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-44600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-40100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-79100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-36900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>20800</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
@@ -6216,14 +6446,17 @@
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,31 +6482,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-300</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E96" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="F96" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="G96" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="H96" s="3">
-        <v>-400</v>
+        <v>300</v>
       </c>
       <c r="I96" s="3">
-        <v>-400</v>
+        <v>400</v>
       </c>
       <c r="J96" s="3">
-        <v>-400</v>
+        <v>400</v>
       </c>
       <c r="K96" s="3">
         <v>-400</v>
@@ -6282,17 +6516,17 @@
         <v>-400</v>
       </c>
       <c r="M96" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N96" s="3">
         <v>-200</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-4600</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,56 +6776,59 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>-14500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>7600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>16600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-22700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>21300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>36600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>10400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>70500</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6598,37 +6844,40 @@
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6675,56 +6924,59 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>700</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-17000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-22100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-67300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-40800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>93300</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6740,10 +6992,13 @@
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
+      <c r="X102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WMPN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WMPN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>WMPN</t>
   </si>
@@ -656,192 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42004</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>41912</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>41729</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6000</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>6200</v>
       </c>
       <c r="R8" s="3">
         <v>6200</v>
       </c>
       <c r="S8" s="3">
+        <v>6200</v>
+      </c>
+      <c r="T8" s="3">
         <v>6800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3200</v>
-      </c>
-      <c r="X8" s="3">
-        <v>3100</v>
       </c>
       <c r="Y8" s="3">
         <v>3100</v>
       </c>
       <c r="Z8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AA8" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -914,35 +920,38 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -988,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1090,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,13 +1180,16 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>700</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1190,8 +1209,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1238,8 +1257,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1259,19 +1281,19 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>-100</v>
@@ -1300,8 +1322,8 @@
       <c r="V15" s="3">
         <v>-100</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
+      <c r="W15" s="3">
+        <v>-100</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>5</v>
@@ -1312,8 +1334,11 @@
       <c r="Z15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,70 +1362,71 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E17" s="3">
         <v>5300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>5200</v>
       </c>
       <c r="I17" s="3">
         <v>5200</v>
       </c>
       <c r="J17" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K17" s="3">
         <v>5500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>600</v>
-      </c>
-      <c r="O17" s="3">
-        <v>700</v>
       </c>
       <c r="P17" s="3">
         <v>700</v>
       </c>
       <c r="Q17" s="3">
+        <v>700</v>
+      </c>
+      <c r="R17" s="3">
         <v>800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1300</v>
-      </c>
-      <c r="W17" s="3">
-        <v>1000</v>
       </c>
       <c r="X17" s="3">
         <v>1000</v>
@@ -1409,75 +1435,78 @@
         <v>1000</v>
       </c>
       <c r="Z17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA17" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2200</v>
-      </c>
-      <c r="X18" s="3">
-        <v>2100</v>
       </c>
       <c r="Y18" s="3">
         <v>2100</v>
@@ -1485,8 +1514,11 @@
       <c r="Z18" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,8 +1545,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1540,106 +1573,109 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-4800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-4200</v>
       </c>
       <c r="P20" s="3">
         <v>-4200</v>
       </c>
       <c r="Q20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="R20" s="3">
         <v>-4600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1661,8 +1697,11 @@
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1687,8 +1726,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1735,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-300</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-100</v>
       </c>
       <c r="G23" s="3">
         <v>-100</v>
       </c>
       <c r="H23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I23" s="3">
         <v>200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1000</v>
-      </c>
-      <c r="W23" s="3">
-        <v>900</v>
       </c>
       <c r="X23" s="3">
         <v>900</v>
       </c>
       <c r="Y23" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z23" s="3">
         <v>1500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E24" s="3">
         <v>-100</v>
       </c>
       <c r="F24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
-      </c>
-      <c r="W24" s="3">
-        <v>300</v>
       </c>
       <c r="X24" s="3">
         <v>300</v>
       </c>
       <c r="Y24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z24" s="3">
         <v>500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>100</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>800</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1200</v>
       </c>
       <c r="P26" s="3">
         <v>1200</v>
       </c>
       <c r="Q26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>800</v>
-      </c>
-      <c r="W26" s="3">
-        <v>600</v>
       </c>
       <c r="X26" s="3">
         <v>600</v>
       </c>
       <c r="Y26" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z26" s="3">
         <v>1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>100</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>800</v>
-      </c>
-      <c r="O27" s="3">
-        <v>1200</v>
       </c>
       <c r="P27" s="3">
         <v>1200</v>
       </c>
       <c r="Q27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>800</v>
-      </c>
-      <c r="W27" s="3">
-        <v>600</v>
       </c>
       <c r="X27" s="3">
         <v>600</v>
       </c>
       <c r="Y27" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z27" s="3">
         <v>1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,8 +2467,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2428,129 +2497,135 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>4800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>4200</v>
       </c>
       <c r="P32" s="3">
         <v>4200</v>
       </c>
       <c r="Q32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="R32" s="3">
         <v>4600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>100</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>800</v>
-      </c>
-      <c r="O33" s="3">
-        <v>1200</v>
       </c>
       <c r="P33" s="3">
         <v>1200</v>
       </c>
       <c r="Q33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>800</v>
-      </c>
-      <c r="W33" s="3">
-        <v>600</v>
       </c>
       <c r="X33" s="3">
         <v>600</v>
       </c>
       <c r="Y33" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z33" s="3">
         <v>1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>100</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>800</v>
-      </c>
-      <c r="O35" s="3">
-        <v>1200</v>
       </c>
       <c r="P35" s="3">
         <v>1200</v>
       </c>
       <c r="Q35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>800</v>
-      </c>
-      <c r="W35" s="3">
-        <v>600</v>
       </c>
       <c r="X35" s="3">
         <v>600</v>
       </c>
       <c r="Y35" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z35" s="3">
         <v>1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42004</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>41912</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>41729</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E41" s="3">
         <v>26500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>23600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>17000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8800</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W41" s="3">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>8800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>13300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2927,41 +3016,41 @@
         <v>100</v>
       </c>
       <c r="I42" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3">
         <v>600</v>
       </c>
       <c r="K42" s="3">
+        <v>600</v>
+      </c>
+      <c r="L42" s="3">
         <v>15400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>14000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>32500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>48100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>58300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>123500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>162400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>175900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>68100</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>5</v>
       </c>
@@ -2980,8 +3069,11 @@
       <c r="Z42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3006,8 +3098,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3054,8 +3146,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3080,8 +3175,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3128,35 +3223,38 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E45" s="3">
         <v>7100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -3202,35 +3300,38 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E46" s="3">
         <v>33800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>27200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25500</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -3276,52 +3377,55 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>234800</v>
+      </c>
+      <c r="E47" s="3">
         <v>245700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>248900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>257300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>262500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>258600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>269000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>277300</v>
-      </c>
-      <c r="K47" s="3">
-        <v>2000</v>
       </c>
       <c r="L47" s="3">
         <v>2000</v>
       </c>
       <c r="M47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N47" s="3">
         <v>2300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2400</v>
-      </c>
-      <c r="O47" s="3">
-        <v>2600</v>
       </c>
       <c r="P47" s="3">
         <v>2600</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
+      <c r="Q47" s="3">
+        <v>2600</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>5</v>
@@ -3338,8 +3442,8 @@
       <c r="V47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3350,61 +3454,64 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E48" s="3">
         <v>15200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>18000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18500</v>
-      </c>
-      <c r="N48" s="3">
-        <v>13400</v>
       </c>
       <c r="O48" s="3">
         <v>13400</v>
       </c>
       <c r="P48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="Q48" s="3">
         <v>13500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13400</v>
-      </c>
-      <c r="R48" s="3">
-        <v>13500</v>
       </c>
       <c r="S48" s="3">
         <v>13500</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
+      <c r="T48" s="3">
+        <v>13500</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
@@ -3424,19 +3531,22 @@
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="E49" s="3">
         <v>5200</v>
       </c>
       <c r="F49" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="G49" s="3">
         <v>5300</v>
@@ -3445,40 +3555,40 @@
         <v>5300</v>
       </c>
       <c r="I49" s="3">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="J49" s="3">
         <v>5400</v>
       </c>
       <c r="K49" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="L49" s="3">
         <v>5500</v>
       </c>
       <c r="M49" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="N49" s="3">
         <v>5600</v>
       </c>
       <c r="O49" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="P49" s="3">
         <v>5700</v>
       </c>
       <c r="Q49" s="3">
+        <v>5700</v>
+      </c>
+      <c r="R49" s="3">
         <v>5800</v>
-      </c>
-      <c r="R49" s="3">
-        <v>5900</v>
       </c>
       <c r="S49" s="3">
         <v>5900</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
+      <c r="T49" s="3">
+        <v>5900</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
@@ -3498,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,62 +3762,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E52" s="3">
         <v>42100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>41800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>41500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>40600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>40300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3720,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>796400</v>
+      </c>
+      <c r="E54" s="3">
         <v>812200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>818700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>833200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>826000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>830000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>847600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>862400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>870900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>851500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>880000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>869000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>834000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>822900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>822400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>817400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>746500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>323800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>315300</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W54" s="3">
-        <v>315300</v>
+      <c r="W54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X54" s="3">
         <v>315300</v>
       </c>
       <c r="Y54" s="3">
+        <v>315300</v>
+      </c>
+      <c r="Z54" s="3">
         <v>311500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>311100</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,35 +4053,36 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>629800</v>
+        <v>627400</v>
       </c>
       <c r="E57" s="3">
         <v>629800</v>
       </c>
       <c r="F57" s="3">
+        <v>629800</v>
+      </c>
+      <c r="G57" s="3">
         <v>625800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>626700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>626500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>635300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>632700</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -3998,35 +4128,38 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E58" s="3">
         <v>39000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>48800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>65000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>54000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>51800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>34000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>38800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4072,8 +4205,11 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4098,36 +4234,36 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>13600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4146,35 +4282,38 @@
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>660800</v>
+      </c>
+      <c r="E60" s="3">
         <v>674000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>683500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>696000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>685800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>683700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>674500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>676900</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -4220,35 +4359,38 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E61" s="3">
         <v>8400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4294,35 +4436,38 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -4368,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,62 +4744,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>672200</v>
+      </c>
+      <c r="E66" s="3">
         <v>684000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>694100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>707400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>697100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>693600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>686800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>688300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>691700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>670300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>687600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>662700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>620100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>609900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>605500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>602400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>649300</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4664,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,62 +5158,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E72" s="3">
         <v>57300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>57600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>58100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>58400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>58800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>58600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>58900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>58200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>57600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>56900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>56300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>55100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>58500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>57800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>56800</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5062,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>124200</v>
+      </c>
+      <c r="E76" s="3">
         <v>128300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>124600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>125800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>128900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>136400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>160700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>174000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>179200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>181200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>192300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>206300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>213900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>213000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>216900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>215000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>97200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>59200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>58400</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W76" s="3">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>58400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>60000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>59800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42004</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>41912</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>41729</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>41639</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>100</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>800</v>
-      </c>
-      <c r="O81" s="3">
-        <v>1200</v>
       </c>
       <c r="P81" s="3">
         <v>1200</v>
       </c>
       <c r="Q81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>800</v>
-      </c>
-      <c r="W81" s="3">
-        <v>600</v>
       </c>
       <c r="X81" s="3">
         <v>600</v>
       </c>
       <c r="Y81" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z81" s="3">
         <v>1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5628,7 +5826,7 @@
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>300</v>
@@ -5640,10 +5838,10 @@
         <v>300</v>
       </c>
       <c r="K83" s="3">
+        <v>300</v>
+      </c>
+      <c r="L83" s="3">
         <v>400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>300</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
@@ -5663,8 +5861,8 @@
       <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
+      <c r="S83" s="3">
+        <v>300</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
@@ -5681,14 +5879,17 @@
       <c r="X83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,59 +6270,62 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2100</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
@@ -6125,14 +6341,17 @@
       <c r="X89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,31 +6378,32 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -6192,7 +6412,7 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>-200</v>
@@ -6201,17 +6421,17 @@
         <v>-200</v>
       </c>
       <c r="P91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6227,14 +6447,17 @@
       <c r="X91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,59 +6607,62 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
         <v>16800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6900</v>
-      </c>
-      <c r="G94" s="3">
-        <v>10300</v>
       </c>
       <c r="H94" s="3">
         <v>10300</v>
       </c>
       <c r="I94" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J94" s="3">
         <v>12000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>12300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-44600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-40100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-79100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-36900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>20800</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
@@ -6449,14 +6678,17 @@
       <c r="X94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,16 +6715,17 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E96" s="3">
-        <v>300</v>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F96" s="3">
         <v>300</v>
@@ -6504,13 +6737,13 @@
         <v>300</v>
       </c>
       <c r="I96" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J96" s="3">
         <v>400</v>
       </c>
       <c r="K96" s="3">
-        <v>-400</v>
+        <v>400</v>
       </c>
       <c r="L96" s="3">
         <v>-400</v>
@@ -6519,17 +6752,17 @@
         <v>-400</v>
       </c>
       <c r="N96" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O96" s="3">
         <v>-200</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,59 +7021,62 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
         <v>-14500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-11900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>16600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-22700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>21300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>36600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>10400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>70500</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6847,14 +7092,17 @@
       <c r="X100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6879,8 +7127,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6927,8 +7175,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6936,50 +7187,50 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>700</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-17000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-22100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-67300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-40800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>93300</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6995,10 +7246,13 @@
       <c r="X102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>
